--- a/nr-init/ig/CodeSystem-cs-fr-FR-administrative-gender.xlsx
+++ b/nr-init/ig/CodeSystem-cs-fr-FR-administrative-gender.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T14:16:52+00:00</t>
+    <t>2025-12-22T14:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
